--- a/healthcare_forms/006_ivf_patient_information_form--healthcare_forms.xlsx
+++ b/healthcare_forms/006_ivf_patient_information_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_121,_'label':_'i_have_read_and_understood_the_consent_form'}</t>
+          <t>i_have_read_and_understood_the_consent_form</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 121, 'label': 'I have read and understood the consent form'}</t>
+          <t>I have read and understood the consent form</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_122}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 122}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_123,_'label':_'i_have_not_read_and_understood_the_consent_form'}</t>
+          <t>i_have_not_read_and_understood_the_consent_form</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 123, 'label': 'I have not read and understood the consent form'}</t>
+          <t>I have not read and understood the consent form</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_131,_'label':_'gynecologist'}</t>
+          <t>gynecologist</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 131, 'label': 'Gynecologist'}</t>
+          <t>Gynecologist</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_132,_'label':_'urologist'}</t>
+          <t>urologist</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 132, 'label': 'Urologist'}</t>
+          <t>Urologist</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_133,_'label':_'cardiologist'}</t>
+          <t>cardiologist</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 133, 'label': 'Cardiologist'}</t>
+          <t>Cardiologist</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_134,_'label':_'nephrologist'}</t>
+          <t>nephrologist</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 134, 'label': 'Nephrologist'}</t>
+          <t>Nephrologist</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_135,_'label':_'gastroenterologist'}</t>
+          <t>gastroenterologist</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 135, 'label': 'Gastroenterologist'}</t>
+          <t>Gastroenterologist</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_141,_'label':_'private_insurance'}</t>
+          <t>private_insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 141, 'label': 'Private Insurance'}</t>
+          <t>Private Insurance</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_142,_'label':_'public_insurance'}</t>
+          <t>public_insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 142, 'label': 'Public Insurance'}</t>
+          <t>Public Insurance</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_143,_'label':_'no_insurance'}</t>
+          <t>no_insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 143, 'label': 'No Insurance'}</t>
+          <t>No Insurance</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_151,_'label':_'ultrasound'}</t>
+          <t>ultrasound</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 151, 'label': 'Ultrasound'}</t>
+          <t>Ultrasound</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_152,_'label':_'blood_test'}</t>
+          <t>blood_test</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 152, 'label': 'Blood test'}</t>
+          <t>Blood test</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_153,_'label':_'x-ray'}</t>
+          <t>x-ray</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 153, 'label': 'X-ray'}</t>
+          <t>X-ray</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_161,_'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 161, 'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_162,_'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 162, 'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_163,_'label':_'ab'}</t>
+          <t>ab</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 163, 'label': 'AB'}</t>
+          <t>AB</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_164,_'label':_'o'}</t>
+          <t>o</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 164, 'label': 'O'}</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_221,_'label':_'gynecologist_2'}</t>
+          <t>gynecologist_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 221, 'label': 'Gynecologist 2'}</t>
+          <t>Gynecologist 2</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_222,_'label':_'urologist_2'}</t>
+          <t>urologist_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 222, 'label': 'Urologist 2'}</t>
+          <t>Urologist 2</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_223,_'label':_'cardiologist_2'}</t>
+          <t>cardiologist_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 223, 'label': 'Cardiologist 2'}</t>
+          <t>Cardiologist 2</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_224,_'label':_'nephrologist_2'}</t>
+          <t>nephrologist_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 224, 'label': 'Nephrologist 2'}</t>
+          <t>Nephrologist 2</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_225,_'label':_'gastroenterologist_2'}</t>
+          <t>gastroenterologist_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 225, 'label': 'Gastroenterologist 2'}</t>
+          <t>Gastroenterologist 2</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_231,_'label':_'ultrasound_2'}</t>
+          <t>ultrasound_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 231, 'label': 'Ultrasound 2'}</t>
+          <t>Ultrasound 2</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_232,_'label':_'blood_test_2'}</t>
+          <t>blood_test_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 232, 'label': 'Blood test 2'}</t>
+          <t>Blood test 2</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_233,_'label':_'x-ray_2'}</t>
+          <t>x-ray_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 233, 'label': 'X-ray 2'}</t>
+          <t>X-ray 2</t>
         </is>
       </c>
     </row>
